--- a/public/plantilla-costos-rentab.xlsx
+++ b/public/plantilla-costos-rentab.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="7" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="7" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Costos y Rentabilidad" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,10 +16,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,6 +115,11 @@
       <i val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -311,7 +316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -334,53 +339,53 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -428,17 +433,17 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -451,7 +456,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -466,13 +471,13 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -502,10 +507,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -523,13 +528,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -539,58 +544,97 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -960,6 +1004,8 @@
     <col width="14" customWidth="1" style="37" min="5" max="5"/>
     <col width="25.77734375" customWidth="1" style="37" min="6" max="6"/>
     <col width="14" customWidth="1" style="37" min="7" max="9"/>
+    <col width="13" customWidth="1" style="37" min="8" max="8"/>
+    <col width="13" customWidth="1" style="37" min="9" max="9"/>
     <col width="15.77734375" customWidth="1" style="37" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -1097,8 +1143,8 @@
       </c>
       <c r="B10" s="100" t="n"/>
       <c r="C10" s="87" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="87" t="n"/>
+      <c r="D10" s="108" t="n"/>
+      <c r="E10" s="109" t="n"/>
       <c r="F10" s="25" t="inlineStr">
         <is>
           <t>Tipo de proyecto</t>
@@ -1106,8 +1152,8 @@
       </c>
       <c r="G10" s="100" t="n"/>
       <c r="H10" s="87" t="n"/>
-      <c r="I10" s="27" t="n"/>
-      <c r="J10" s="87" t="n"/>
+      <c r="I10" s="108" t="n"/>
+      <c r="J10" s="109" t="n"/>
     </row>
     <row r="11" ht="18" customHeight="1" s="37">
       <c r="A11" s="25" t="inlineStr">
@@ -1117,8 +1163,8 @@
       </c>
       <c r="B11" s="100" t="n"/>
       <c r="C11" s="87" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="87" t="n"/>
+      <c r="D11" s="108" t="n"/>
+      <c r="E11" s="109" t="n"/>
       <c r="F11" s="25" t="inlineStr">
         <is>
           <t>Contratante</t>
@@ -1126,8 +1172,8 @@
       </c>
       <c r="G11" s="100" t="n"/>
       <c r="H11" s="87" t="n"/>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="87" t="n"/>
+      <c r="I11" s="108" t="n"/>
+      <c r="J11" s="109" t="n"/>
     </row>
     <row r="12" ht="18" customHeight="1" s="37">
       <c r="A12" s="25" t="inlineStr">
@@ -1137,8 +1183,8 @@
       </c>
       <c r="B12" s="100" t="n"/>
       <c r="C12" s="87" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="87" t="n"/>
+      <c r="D12" s="108" t="n"/>
+      <c r="E12" s="109" t="n"/>
       <c r="F12" s="25" t="inlineStr">
         <is>
           <t>Responsable del informe</t>
@@ -1146,8 +1192,8 @@
       </c>
       <c r="G12" s="100" t="n"/>
       <c r="H12" s="87" t="n"/>
-      <c r="I12" s="27" t="n"/>
-      <c r="J12" s="87" t="n"/>
+      <c r="I12" s="108" t="n"/>
+      <c r="J12" s="109" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="37">
       <c r="A13" s="43" t="inlineStr">
@@ -1165,7 +1211,7 @@
       <c r="I13" s="100" t="n"/>
       <c r="J13" s="87" t="n"/>
     </row>
-    <row r="14" ht="18" customHeight="1" s="37">
+    <row r="14" ht="55" customHeight="1" s="37">
       <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Valor del contrato inicial</t>
@@ -1173,8 +1219,8 @@
       </c>
       <c r="B14" s="100" t="n"/>
       <c r="C14" s="87" t="n"/>
-      <c r="D14" s="47" t="n"/>
-      <c r="F14" s="27" t="inlineStr">
+      <c r="D14" s="110" t="n"/>
+      <c r="F14" s="111" t="inlineStr">
         <is>
           <t>Valor del contrato y adicionales: tomados del contrato y del formato de Adicionales (los aprobados).
 Facturado: suma de las actas de cobro (valor bruto).
@@ -1194,7 +1240,7 @@
       </c>
       <c r="B15" s="100" t="n"/>
       <c r="C15" s="87" t="n"/>
-      <c r="D15" s="47" t="n"/>
+      <c r="D15" s="110" t="n"/>
       <c r="F15" s="52" t="n"/>
       <c r="J15" s="53" t="n"/>
     </row>
@@ -1206,7 +1252,7 @@
       </c>
       <c r="B16" s="100" t="n"/>
       <c r="C16" s="87" t="n"/>
-      <c r="D16" s="98">
+      <c r="D16" s="112">
         <f>N(D14)+N(D15)</f>
         <v/>
       </c>
@@ -1221,7 +1267,7 @@
       </c>
       <c r="B17" s="100" t="n"/>
       <c r="C17" s="87" t="n"/>
-      <c r="D17" s="47" t="n"/>
+      <c r="D17" s="110" t="n"/>
       <c r="F17" s="52" t="n"/>
       <c r="J17" s="53" t="n"/>
     </row>
@@ -1233,7 +1279,7 @@
       </c>
       <c r="B18" s="100" t="n"/>
       <c r="C18" s="87" t="n"/>
-      <c r="D18" s="99">
+      <c r="D18" s="113">
         <f>IF(N(D16)=0,"",D17/D16)</f>
         <v/>
       </c>
@@ -1305,7 +1351,7 @@
       <c r="J21" s="87" t="n"/>
     </row>
     <row r="22" ht="19.95" customHeight="1" s="37">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="114" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="25" t="inlineStr">
@@ -1313,17 +1359,17 @@
           <t>Material</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="101">
+      <c r="C22" s="110" t="n"/>
+      <c r="D22" s="110" t="n"/>
+      <c r="E22" s="115">
         <f>IF(OR(D22="",D29=0),"",D22/D29)</f>
         <v/>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="116">
         <f>IF(OR(C22="",D22=""),"",D22-C22)</f>
         <v/>
       </c>
-      <c r="G22" s="101">
+      <c r="G22" s="115">
         <f>IF(OR(C22="",C22=0,D22=""),"",D22/C22-1)</f>
         <v/>
       </c>
@@ -1335,7 +1381,7 @@
       <c r="J22" s="87" t="n"/>
     </row>
     <row r="23" ht="19.95" customHeight="1" s="37">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="114" t="n">
         <v>2</v>
       </c>
       <c r="B23" s="25" t="inlineStr">
@@ -1343,17 +1389,17 @@
           <t>Mano de obra</t>
         </is>
       </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="101">
+      <c r="C23" s="110" t="n"/>
+      <c r="D23" s="110" t="n"/>
+      <c r="E23" s="115">
         <f>IF(OR(D23="",D29=0),"",D23/D29)</f>
         <v/>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="116">
         <f>IF(OR(C23="",D23=""),"",D23-C23)</f>
         <v/>
       </c>
-      <c r="G23" s="101">
+      <c r="G23" s="115">
         <f>IF(OR(C23="",C23=0,D23=""),"",D23/C23-1)</f>
         <v/>
       </c>
@@ -1365,7 +1411,7 @@
       <c r="J23" s="87" t="n"/>
     </row>
     <row r="24" ht="19.95" customHeight="1" s="37">
-      <c r="A24" s="6" t="n">
+      <c r="A24" s="114" t="n">
         <v>3</v>
       </c>
       <c r="B24" s="25" t="inlineStr">
@@ -1373,17 +1419,17 @@
           <t>Subcontrato</t>
         </is>
       </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="101">
+      <c r="C24" s="110" t="n"/>
+      <c r="D24" s="110" t="n"/>
+      <c r="E24" s="115">
         <f>IF(OR(D24="",D29=0),"",D24/D29)</f>
         <v/>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="116">
         <f>IF(OR(C24="",D24=""),"",D24-C24)</f>
         <v/>
       </c>
-      <c r="G24" s="101">
+      <c r="G24" s="115">
         <f>IF(OR(C24="",C24=0,D24=""),"",D24/C24-1)</f>
         <v/>
       </c>
@@ -1395,7 +1441,7 @@
       <c r="J24" s="87" t="n"/>
     </row>
     <row r="25" ht="19.95" customHeight="1" s="37">
-      <c r="A25" s="6" t="n">
+      <c r="A25" s="114" t="n">
         <v>4</v>
       </c>
       <c r="B25" s="25" t="inlineStr">
@@ -1403,17 +1449,17 @@
           <t>Maquinaria y equipo</t>
         </is>
       </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="101">
+      <c r="C25" s="110" t="n"/>
+      <c r="D25" s="110" t="n"/>
+      <c r="E25" s="115">
         <f>IF(OR(D25="",D29=0),"",D25/D29)</f>
         <v/>
       </c>
-      <c r="F25" s="9">
+      <c r="F25" s="116">
         <f>IF(OR(C25="",D25=""),"",D25-C25)</f>
         <v/>
       </c>
-      <c r="G25" s="101">
+      <c r="G25" s="115">
         <f>IF(OR(C25="",C25=0,D25=""),"",D25/C25-1)</f>
         <v/>
       </c>
@@ -1425,7 +1471,7 @@
       <c r="J25" s="87" t="n"/>
     </row>
     <row r="26" ht="19.95" customHeight="1" s="37">
-      <c r="A26" s="6" t="n">
+      <c r="A26" s="114" t="n">
         <v>5</v>
       </c>
       <c r="B26" s="25" t="inlineStr">
@@ -1433,17 +1479,17 @@
           <t>Transporte</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="101">
+      <c r="C26" s="110" t="n"/>
+      <c r="D26" s="110" t="n"/>
+      <c r="E26" s="115">
         <f>IF(OR(D26="",D29=0),"",D26/D29)</f>
         <v/>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="116">
         <f>IF(OR(C26="",D26=""),"",D26-C26)</f>
         <v/>
       </c>
-      <c r="G26" s="101">
+      <c r="G26" s="115">
         <f>IF(OR(C26="",C26=0,D26=""),"",D26/C26-1)</f>
         <v/>
       </c>
@@ -1455,7 +1501,7 @@
       <c r="J26" s="87" t="n"/>
     </row>
     <row r="27" ht="19.95" customHeight="1" s="37">
-      <c r="A27" s="6" t="n">
+      <c r="A27" s="114" t="n">
         <v>6</v>
       </c>
       <c r="B27" s="25" t="inlineStr">
@@ -1463,17 +1509,17 @@
           <t>Administración</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="101">
+      <c r="C27" s="110" t="n"/>
+      <c r="D27" s="110" t="n"/>
+      <c r="E27" s="115">
         <f>IF(OR(D27="",D29=0),"",D27/D29)</f>
         <v/>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="116">
         <f>IF(OR(C27="",D27=""),"",D27-C27)</f>
         <v/>
       </c>
-      <c r="G27" s="101">
+      <c r="G27" s="115">
         <f>IF(OR(C27="",C27=0,D27=""),"",D27/C27-1)</f>
         <v/>
       </c>
@@ -1485,7 +1531,7 @@
       <c r="J27" s="87" t="n"/>
     </row>
     <row r="28" ht="19.95" customHeight="1" s="37">
-      <c r="A28" s="6" t="n">
+      <c r="A28" s="114" t="n">
         <v>7</v>
       </c>
       <c r="B28" s="25" t="inlineStr">
@@ -1493,17 +1539,17 @@
           <t>Otro</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="101">
+      <c r="C28" s="110" t="n"/>
+      <c r="D28" s="110" t="n"/>
+      <c r="E28" s="115">
         <f>IF(OR(D28="",D29=0),"",D28/D29)</f>
         <v/>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="116">
         <f>IF(OR(C28="",D28=""),"",D28-C28)</f>
         <v/>
       </c>
-      <c r="G28" s="101">
+      <c r="G28" s="115">
         <f>IF(OR(C28="",C28=0,D28=""),"",D28/C28-1)</f>
         <v/>
       </c>
@@ -1521,23 +1567,23 @@
         </is>
       </c>
       <c r="B29" s="87" t="n"/>
-      <c r="C29" s="89">
+      <c r="C29" s="117">
         <f>IF(COUNT(C22:C28)=0,"",SUM(C22:C28))</f>
         <v/>
       </c>
-      <c r="D29" s="89">
+      <c r="D29" s="117">
         <f>SUM(D22:D28)</f>
         <v/>
       </c>
-      <c r="E29" s="85">
+      <c r="E29" s="118">
         <f>IF(D29=0,"",1)</f>
         <v/>
       </c>
-      <c r="F29" s="89">
+      <c r="F29" s="117">
         <f>IF(C29="","",SUMIF(C22:C28,"&lt;&gt;",D22:D28)-C29)</f>
         <v/>
       </c>
-      <c r="G29" s="85">
+      <c r="G29" s="118">
         <f>IF(OR(C29="",C29=0),"",SUMIF(C22:C28,"&lt;&gt;",D22:D28)/C29-1)</f>
         <v/>
       </c>
@@ -1565,7 +1611,7 @@
       <c r="I31" s="100" t="n"/>
       <c r="J31" s="87" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1" s="37">
+    <row r="32" ht="146" customHeight="1" s="37">
       <c r="A32" s="25" t="inlineStr">
         <is>
           <t>Costo real a la fecha</t>
@@ -1573,11 +1619,11 @@
       </c>
       <c r="B32" s="100" t="n"/>
       <c r="C32" s="87" t="n"/>
-      <c r="D32" s="98">
+      <c r="D32" s="112">
         <f>D29</f>
         <v/>
       </c>
-      <c r="F32" s="27" t="inlineStr">
+      <c r="F32" s="111" t="inlineStr">
         <is>
           <t>Costo estimado por terminar: lo que falta gastar para entregar la obra (lo estima el director de obra).
 Utilidad proyectada = valor vigente del contrato − costo proyectado al cierre.
@@ -1602,7 +1648,7 @@
       </c>
       <c r="B33" s="100" t="n"/>
       <c r="C33" s="87" t="n"/>
-      <c r="D33" s="98">
+      <c r="D33" s="112">
         <f>IF(N(D17)=0,"",D17-D32)</f>
         <v/>
       </c>
@@ -1617,7 +1663,7 @@
       </c>
       <c r="B34" s="100" t="n"/>
       <c r="C34" s="87" t="n"/>
-      <c r="D34" s="99">
+      <c r="D34" s="113">
         <f>IF(N(D17)=0,"",D33/D17)</f>
         <v/>
       </c>
@@ -1632,7 +1678,7 @@
       </c>
       <c r="B35" s="100" t="n"/>
       <c r="C35" s="87" t="n"/>
-      <c r="D35" s="48" t="n"/>
+      <c r="D35" s="119" t="n"/>
       <c r="F35" s="52" t="n"/>
       <c r="J35" s="53" t="n"/>
     </row>
@@ -1644,7 +1690,7 @@
       </c>
       <c r="B36" s="100" t="n"/>
       <c r="C36" s="87" t="n"/>
-      <c r="D36" s="47" t="n"/>
+      <c r="D36" s="110" t="n"/>
       <c r="F36" s="52" t="n"/>
       <c r="J36" s="53" t="n"/>
     </row>
@@ -1656,7 +1702,7 @@
       </c>
       <c r="B37" s="100" t="n"/>
       <c r="C37" s="87" t="n"/>
-      <c r="D37" s="98">
+      <c r="D37" s="112">
         <f>IF(D36="","",D32+D36)</f>
         <v/>
       </c>
@@ -1671,7 +1717,7 @@
       </c>
       <c r="B38" s="100" t="n"/>
       <c r="C38" s="87" t="n"/>
-      <c r="D38" s="98">
+      <c r="D38" s="112">
         <f>IF(OR(D37="",N(D16)=0),"",D16-D37)</f>
         <v/>
       </c>
@@ -1686,7 +1732,7 @@
       </c>
       <c r="B39" s="100" t="n"/>
       <c r="C39" s="87" t="n"/>
-      <c r="D39" s="99">
+      <c r="D39" s="113">
         <f>IF(D38="","",D38/D16)</f>
         <v/>
       </c>
@@ -1701,7 +1747,7 @@
       </c>
       <c r="B40" s="100" t="n"/>
       <c r="C40" s="87" t="n"/>
-      <c r="D40" s="48" t="n"/>
+      <c r="D40" s="119" t="n"/>
       <c r="F40" s="52" t="n"/>
       <c r="J40" s="53" t="n"/>
     </row>
@@ -1768,8 +1814,8 @@
       </c>
       <c r="B45" s="100" t="n"/>
       <c r="C45" s="87" t="n"/>
-      <c r="D45" s="27" t="n"/>
-      <c r="E45" s="87" t="n"/>
+      <c r="D45" s="108" t="n"/>
+      <c r="E45" s="109" t="n"/>
       <c r="F45" s="25" t="inlineStr">
         <is>
           <t>Firma:</t>
@@ -1777,8 +1823,8 @@
       </c>
       <c r="G45" s="100" t="n"/>
       <c r="H45" s="87" t="n"/>
-      <c r="I45" s="27" t="n"/>
-      <c r="J45" s="87" t="n"/>
+      <c r="I45" s="108" t="n"/>
+      <c r="J45" s="109" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="37">
       <c r="A46" s="25" t="inlineStr">
@@ -1788,8 +1834,8 @@
       </c>
       <c r="B46" s="100" t="n"/>
       <c r="C46" s="87" t="n"/>
-      <c r="D46" s="27" t="n"/>
-      <c r="E46" s="87" t="n"/>
+      <c r="D46" s="108" t="n"/>
+      <c r="E46" s="109" t="n"/>
       <c r="F46" s="25" t="inlineStr">
         <is>
           <t>Nombre:</t>
@@ -1797,8 +1843,8 @@
       </c>
       <c r="G46" s="100" t="n"/>
       <c r="H46" s="87" t="n"/>
-      <c r="I46" s="27" t="n"/>
-      <c r="J46" s="87" t="n"/>
+      <c r="I46" s="108" t="n"/>
+      <c r="J46" s="109" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1" s="37">
       <c r="A47" s="25" t="inlineStr">
@@ -1808,8 +1854,8 @@
       </c>
       <c r="B47" s="100" t="n"/>
       <c r="C47" s="87" t="n"/>
-      <c r="D47" s="27" t="n"/>
-      <c r="E47" s="87" t="n"/>
+      <c r="D47" s="108" t="n"/>
+      <c r="E47" s="109" t="n"/>
       <c r="F47" s="25" t="inlineStr">
         <is>
           <t>Cargo:</t>
@@ -1817,10 +1863,11 @@
       </c>
       <c r="G47" s="100" t="n"/>
       <c r="H47" s="87" t="n"/>
-      <c r="I47" s="27" t="n"/>
-      <c r="J47" s="87" t="n"/>
+      <c r="I47" s="108" t="n"/>
+      <c r="J47" s="109" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="71">
     <mergeCell ref="F44:J44"/>
     <mergeCell ref="A41:C41"/>
